--- a/Results/single_algorithm/CIMLR/CIMLR_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/single_algorithm/CIMLR/CIMLR_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -20,1885 +20,1885 @@
     <t xml:space="preserve">Cluster</t>
   </si>
   <si>
+    <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMLRCIMLR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A274-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMLRCIMLR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A247-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A7U7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A278-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3W7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A6R8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0U2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-W8-A86G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A5UO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2BK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-Z7-A8R5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A14N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A24A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-4H-AAAK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1II-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-HN-A2NL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A5IZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA12-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA10-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A244-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A0D9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3Y0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A256-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A243-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A3NW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A2L8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A075-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0WA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0GY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A42V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A9RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A401-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA0Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A229-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA14-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A3X8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A66U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4RW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24M-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A6HE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A128-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A5J0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0U3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A5PV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1QZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A209-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A574-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A3KD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A54Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24S-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A97C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2D9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-V7-A7HQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A3XL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2B8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A7SZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-AB28-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A7W5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A250-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6NO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A8HR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1B4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A226-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A3Z6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A259-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0X5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A28Q-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0CR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A124-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JG-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A255-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-UL-AAZ6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A62X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A7T0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A4SE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A7W6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1BD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A208-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0C3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5S0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-UU-A93S-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A54N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A273-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8G0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-WT-AB44-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0EN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A08O-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A56Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A570-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A50Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1Y1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A254-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1J8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A573-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PE-A5DE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5DA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A202-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A2JT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A203-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1AZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A73Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A5PX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66N-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1L8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A2P5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A56D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5EH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A1-A0SE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A5FL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66P-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-XX-A899-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A04H-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-AA17-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A27A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1OV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A0AD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26V-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A27B-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3OD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A40C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0EU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A295-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A245-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26W-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A1H3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A8-A0A6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1ET-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A227-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A2JS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-5T-A9QA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0X4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0HX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A25D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A201-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-5L-AAT0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-WT-AB41-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13D-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A23C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27M-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-Z7-A8R6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PE-A5DD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A04R-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1PE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-S3-A6ZH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A576-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1ND-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AQ-A1H2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5D7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1N9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A4Z1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1FZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A2IU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0SW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A4S3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22B-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A228-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AAAU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A9Q3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A252-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2FF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A4ZE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A22A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A1G0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2BM-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A6VX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A26G-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1RI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0B5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0GZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0WY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6S9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1X6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-XX-A89A-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A4SF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A740-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1J5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1ES-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A6IX-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A10C-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JA-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A03L-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A73Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A204-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0W4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A5QN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A62Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A7VC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13F-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0H7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1F0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A5YL-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A3YI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8FZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1LK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1P4-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A409-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A248-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0AZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A15K-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AN-A0XO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1NG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A7VB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-3C-AALI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A2FS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1J9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1BC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0BJ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5XS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26Z-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1FN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HG-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A27T-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JS-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R7-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A5ZV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A26Y-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66H-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1JI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RZ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A6R9-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A1EO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DN-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A0TQ-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A8FY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A1IW-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A7-A13E-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XF-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A251-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24X-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R3-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A0RV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OK-A5Q2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R6-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A275-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A8F5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0YK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AK-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66J-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A73U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A5XU-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SC-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A66I-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0DV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0CT-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LD-A74U-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-A2-A0T5-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A1KP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JE-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A6VO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-HN-A2OB-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A1AO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0E1-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A2QH-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-EW-A6SD-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-PL-A8LV-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-OL-A5RY-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AC-A8OP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-LL-A6FP-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GI-A2C8-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A2LR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AO-A0JI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-C8-A1HI-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-BH-A0C0-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-B6-A1KC-01B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-GM-A2DO-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-AR-A24Q-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-D8-A1XR-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E9-A1R2-01A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCGA-E2-A1IG-01A</t>
+  </si>
+  <si>
     <t xml:space="preserve">TCGA-AR-A2LE-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">CIMLR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26Y-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5XS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A10C-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PE-A5DE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1J8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2D9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A128-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A2L8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8FZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AAAU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22B-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66L-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13D-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A295-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A04H-01B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5FL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A97C-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A574-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A5IZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A14N-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2BK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23C-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27N-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2B8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A209-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A243-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0WA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25A-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A24A-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3XU-01A</t>
-  </si>
-  <si>
     <t xml:space="preserve">TCGA-E2-A1IO-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">TCGA-B6-A1KC-01B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-HN-A2OB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6SC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OK-A5Q2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24X-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8FY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27T-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26Z-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1BC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A7VB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15K-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15J-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A73Z-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A03L-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1ES-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A740-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A4SF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24K-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27K-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A4ZE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66K-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A9Q3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A4Z1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A1H2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A576-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PE-A5DD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-WT-AB41-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73X-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A227-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1ET-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A0A6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A1H3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A245-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0EU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A40C-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3OD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A0AD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-XX-A899-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27P-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A2P5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66N-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A5PX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A202-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24N-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5DA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27L-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A50Y-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A570-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A56Z-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A08O-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-WT-AB44-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A8G0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5S0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1BD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A7W6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A7T0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A255-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0W5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A28Q-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0X5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A259-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A3Z6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A226-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6NO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24O-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A5QM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24S-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1L6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1QZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A5PV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A5J0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24M-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A66U-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A3X8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A6FQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA14-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A229-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A401-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A42V-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0GY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25C-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A3NW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A0D9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0BT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24L-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-4H-AAAK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4S2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-Z7-A8R5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A15I-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A6R8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3W7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A278-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A23E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A7U7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A409-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A204-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24W-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A8-A075-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A2IU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-5T-A9QA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24Q-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMLR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0C0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GI-A2C8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A74U-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0CT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73U-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A8F5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A275-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A251-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1IW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A5ZV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1J9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-XX-A89A-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1ND-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A04R-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-5L-AAT0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A27B-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA17-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66P-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5EH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A56D-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A73Y-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27V-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1Y1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-UU-A93S-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A4SE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-UL-AAZ6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JG-01B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A124-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0CR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A250-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27F-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A3XL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A4RW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A256-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3Y0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A244-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA10-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A274-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2QH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66I-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A5XU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66J-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1R7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A6VR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A2FS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24Z-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0AZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A248-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13F-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A7VC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A62Y-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A6IX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A6S9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27I-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0GZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P8-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2BM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22A-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A252-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25D-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A2JS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26W-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A73W-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A27A-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-A6ZF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1AZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A203-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24V-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24U-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A254-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A22D-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0EN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A273-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0C3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24R-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1FG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0YT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A1KS-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1FW-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A8HR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LD-A7W5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0SX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-AB28-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A7SZ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AN-A0XT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A0T1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-V7-A7HQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A54Y-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A3KD-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0U3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A6HE-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-3C-AALJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27R-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1RB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA0Z-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A9RU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A25E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A2-A1G1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A24P-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66O-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-S3-AA12-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1II-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26J-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A5UO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-W8-A86G-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27W-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A247-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WV-01A</t>
-  </si>
-  <si>
     <t xml:space="preserve">TCGA-S3-AA11-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1F2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1N9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5D7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1X5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B3-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1LA-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A2LR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A5RY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A8OR-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A13E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EO-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A6R9-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-OL-A66H-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HG-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A3YI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-LL-A5YL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0H7-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A1HL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0B5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A6VV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A2FF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26I-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-Z7-A8R6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27M-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0HX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0X4-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26V-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AO-A0JJ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1JH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A2JT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0TV-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A573-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AQ-A54N-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A208-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A1KN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0RU-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A27E-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-PL-A8LY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AC-A62X-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A7-A26F-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WT-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1IK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DQ-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-C8-A26X-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-D8-A1XC-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SP-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A1NF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A1AY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DM-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1OY-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0E0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-HN-A2NL-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B0-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-AR-A0U2-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1PH-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-B6-A0WX-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A1EN-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-GM-A2DF-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DI-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-A1-A0SB-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A0DK-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1P5-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-BH-A201-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-EW-A1J6-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E2-A1B1-01A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCGA-E9-A228-01A</t>
   </si>
 </sst>
 </file>
@@ -2256,20 +2256,20 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>3</v>
@@ -2285,7 +2285,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>3</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>3</v>
@@ -2301,7 +2301,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>3</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>3</v>
@@ -2325,7 +2325,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
         <v>3</v>
@@ -2333,7 +2333,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -2341,7 +2341,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
         <v>3</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16" t="s">
         <v>3</v>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
         <v>3</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
         <v>3</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>3</v>
@@ -2381,7 +2381,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
         <v>3</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
         <v>3</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
         <v>3</v>
@@ -2405,7 +2405,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
         <v>3</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>3</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
         <v>3</v>
@@ -2429,7 +2429,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -2437,7 +2437,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>3</v>
@@ -2445,7 +2445,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>3</v>
@@ -2453,23 +2453,23 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
         <v>3</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>3</v>
@@ -2485,15 +2485,15 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>3</v>
@@ -2501,7 +2501,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>3</v>
@@ -2509,15 +2509,15 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
         <v>3</v>
@@ -2525,7 +2525,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
@@ -2533,7 +2533,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
         <v>3</v>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41" t="s">
         <v>3</v>
@@ -2557,7 +2557,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42" t="s">
         <v>3</v>
@@ -2565,7 +2565,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
         <v>3</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B44" t="s">
         <v>3</v>
@@ -2581,7 +2581,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45" t="s">
         <v>3</v>
@@ -2589,7 +2589,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B46" t="s">
         <v>3</v>
@@ -2597,15 +2597,15 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B48" t="s">
         <v>3</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
         <v>3</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B51" t="s">
         <v>3</v>
@@ -2637,7 +2637,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
         <v>3</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
         <v>3</v>
@@ -2653,7 +2653,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B54" t="s">
         <v>3</v>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B55" t="s">
         <v>3</v>
@@ -2669,23 +2669,23 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
         <v>3</v>
@@ -2693,7 +2693,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
         <v>3</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B60" t="s">
         <v>3</v>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
         <v>3</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B62" t="s">
         <v>3</v>
@@ -2725,7 +2725,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B63" t="s">
         <v>3</v>
@@ -2733,15 +2733,15 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B65" t="s">
         <v>3</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
         <v>3</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B67" t="s">
         <v>3</v>
@@ -2765,15 +2765,15 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
         <v>3</v>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B70" t="s">
         <v>3</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B71" t="s">
         <v>3</v>
@@ -2797,15 +2797,15 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B73" t="s">
         <v>3</v>
@@ -2813,7 +2813,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s">
         <v>3</v>
@@ -2821,7 +2821,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B75" t="s">
         <v>3</v>
@@ -2829,7 +2829,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B76" t="s">
         <v>3</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B77" t="s">
         <v>3</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B78" t="s">
         <v>3</v>
@@ -2853,15 +2853,15 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B80" t="s">
         <v>3</v>
@@ -2869,15 +2869,15 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B82" t="s">
         <v>3</v>
@@ -2885,7 +2885,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B83" t="s">
         <v>3</v>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B84" t="s">
         <v>3</v>
@@ -2901,15 +2901,15 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
         <v>3</v>
@@ -2917,7 +2917,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B87" t="s">
         <v>3</v>
@@ -2925,15 +2925,15 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B88" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B89" t="s">
         <v>3</v>
@@ -2941,7 +2941,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B90" t="s">
         <v>3</v>
@@ -2949,15 +2949,15 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B92" t="s">
         <v>3</v>
@@ -2965,7 +2965,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B93" t="s">
         <v>3</v>
@@ -2973,15 +2973,15 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B94" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B95" t="s">
         <v>3</v>
@@ -2989,7 +2989,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B96" t="s">
         <v>3</v>
@@ -2997,7 +2997,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
         <v>3</v>
@@ -3005,7 +3005,7 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B98" t="s">
         <v>3</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B99" t="s">
         <v>3</v>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B100" t="s">
         <v>3</v>
@@ -3029,7 +3029,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B101" t="s">
         <v>3</v>
@@ -3037,7 +3037,7 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B102" t="s">
         <v>3</v>
@@ -3045,7 +3045,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B103" t="s">
         <v>3</v>
@@ -3053,7 +3053,7 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B104" t="s">
         <v>3</v>
@@ -3061,7 +3061,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B105" t="s">
         <v>3</v>
@@ -3069,15 +3069,15 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B107" t="s">
         <v>3</v>
@@ -3085,7 +3085,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B108" t="s">
         <v>3</v>
@@ -3093,7 +3093,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
         <v>3</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B110" t="s">
         <v>3</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B111" t="s">
         <v>3</v>
@@ -3117,7 +3117,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B112" t="s">
         <v>3</v>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B113" t="s">
         <v>3</v>
@@ -3133,15 +3133,15 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B114" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B115" t="s">
         <v>3</v>
@@ -3149,7 +3149,7 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B116" t="s">
         <v>3</v>
@@ -3157,7 +3157,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B117" t="s">
         <v>3</v>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B118" t="s">
         <v>3</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B119" t="s">
         <v>3</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
         <v>3</v>
@@ -3189,15 +3189,15 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B121" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
         <v>3</v>
@@ -3205,7 +3205,7 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
         <v>3</v>
@@ -3213,7 +3213,7 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B124" t="s">
         <v>3</v>
@@ -3221,31 +3221,31 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B125" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B126" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B127" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B128" t="s">
         <v>3</v>
@@ -3253,7 +3253,7 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B129" t="s">
         <v>3</v>
@@ -3261,7 +3261,7 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B130" t="s">
         <v>3</v>
@@ -3269,7 +3269,7 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B131" t="s">
         <v>3</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B132" t="s">
         <v>3</v>
@@ -3285,7 +3285,7 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B133" t="s">
         <v>3</v>
@@ -3293,15 +3293,15 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B134" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B135" t="s">
         <v>3</v>
@@ -3309,7 +3309,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B136" t="s">
         <v>3</v>
@@ -3317,7 +3317,7 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B137" t="s">
         <v>3</v>
@@ -3325,7 +3325,7 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B138" t="s">
         <v>3</v>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B139" t="s">
         <v>3</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B140" t="s">
         <v>3</v>
@@ -3349,7 +3349,7 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B141" t="s">
         <v>3</v>
@@ -3357,15 +3357,15 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B142" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B143" t="s">
         <v>3</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B144" t="s">
         <v>3</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B145" t="s">
         <v>3</v>
@@ -3389,7 +3389,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B146" t="s">
         <v>3</v>
@@ -3397,7 +3397,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B147" t="s">
         <v>3</v>
@@ -3405,7 +3405,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B148" t="s">
         <v>3</v>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B149" t="s">
         <v>3</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B150" t="s">
         <v>3</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B151" t="s">
         <v>3</v>
@@ -3437,7 +3437,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B152" t="s">
         <v>3</v>
@@ -3445,7 +3445,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B153" t="s">
         <v>3</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B154" t="s">
         <v>3</v>
@@ -3461,7 +3461,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B155" t="s">
         <v>3</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B156" t="s">
         <v>3</v>
@@ -3477,15 +3477,15 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B157" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B158" t="s">
         <v>3</v>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B159" t="s">
         <v>3</v>
@@ -3501,7 +3501,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B160" t="s">
         <v>3</v>
@@ -3509,7 +3509,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B161" t="s">
         <v>3</v>
@@ -3517,15 +3517,15 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B162" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B163" t="s">
         <v>3</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B164" t="s">
         <v>3</v>
@@ -3541,7 +3541,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B165" t="s">
         <v>3</v>
@@ -3549,7 +3549,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B166" t="s">
         <v>3</v>
@@ -3557,15 +3557,15 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B167" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B168" t="s">
         <v>3</v>
@@ -3573,7 +3573,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B169" t="s">
         <v>3</v>
@@ -3581,15 +3581,15 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B170" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B171" t="s">
         <v>3</v>
@@ -3597,7 +3597,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B172" t="s">
         <v>3</v>
@@ -3605,15 +3605,15 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B173" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B174" t="s">
         <v>3</v>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B175" t="s">
         <v>3</v>
@@ -3629,7 +3629,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B176" t="s">
         <v>3</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B177" t="s">
         <v>3</v>
@@ -3645,23 +3645,23 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B178" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B179" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B180" t="s">
         <v>3</v>
@@ -3669,7 +3669,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B181" t="s">
         <v>3</v>
@@ -3677,15 +3677,15 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B182" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B183" t="s">
         <v>3</v>
@@ -3693,7 +3693,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B184" t="s">
         <v>3</v>
@@ -3701,15 +3701,15 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B185" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B186" t="s">
         <v>3</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B187" t="s">
         <v>3</v>
@@ -3725,7 +3725,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B188" t="s">
         <v>3</v>
@@ -3733,7 +3733,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B189" t="s">
         <v>3</v>
@@ -3741,7 +3741,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B190" t="s">
         <v>3</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B191" t="s">
         <v>3</v>
@@ -3757,7 +3757,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B192" t="s">
         <v>3</v>
@@ -3765,15 +3765,15 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B193" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B194" t="s">
         <v>3</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B195" t="s">
         <v>3</v>
@@ -3789,15 +3789,15 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B196" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B197" t="s">
         <v>3</v>
@@ -3805,7 +3805,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B198" t="s">
         <v>3</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B199" t="s">
         <v>3</v>
@@ -3821,7 +3821,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B200" t="s">
         <v>3</v>
@@ -3829,23 +3829,23 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B201" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B202" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B203" t="s">
         <v>3</v>
@@ -3853,15 +3853,15 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B204" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B205" t="s">
         <v>3</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B206" t="s">
         <v>3</v>
@@ -3877,7 +3877,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B207" t="s">
         <v>3</v>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B208" t="s">
         <v>3</v>
@@ -3893,7 +3893,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B209" t="s">
         <v>3</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B210" t="s">
         <v>3</v>
@@ -3909,7 +3909,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B211" t="s">
         <v>3</v>
@@ -3917,7 +3917,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B212" t="s">
         <v>3</v>
@@ -3925,7 +3925,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B213" t="s">
         <v>3</v>
@@ -3933,15 +3933,15 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B214" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B215" t="s">
         <v>3</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B216" t="s">
         <v>3</v>
@@ -3957,7 +3957,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B217" t="s">
         <v>3</v>
@@ -3965,7 +3965,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B218" t="s">
         <v>3</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B219" t="s">
         <v>3</v>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B220" t="s">
         <v>3</v>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B221" t="s">
         <v>3</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B222" t="s">
         <v>3</v>
@@ -4005,7 +4005,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B223" t="s">
         <v>3</v>
@@ -4013,7 +4013,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B224" t="s">
         <v>3</v>
@@ -4021,7 +4021,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B225" t="s">
         <v>3</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B226" t="s">
         <v>3</v>
@@ -4037,55 +4037,55 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B227" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B228" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B229" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B230" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B231" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B232" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B233" t="s">
         <v>3</v>
@@ -4093,7 +4093,7 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B234" t="s">
         <v>3</v>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B235" t="s">
         <v>3</v>
@@ -4109,15 +4109,15 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B236" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B237" t="s">
         <v>3</v>
@@ -4125,7 +4125,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B238" t="s">
         <v>3</v>
@@ -4133,7 +4133,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B239" t="s">
         <v>3</v>
@@ -4141,7 +4141,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B240" t="s">
         <v>3</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B241" t="s">
         <v>3</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B242" t="s">
         <v>3</v>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B243" t="s">
         <v>3</v>
@@ -4173,7 +4173,7 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B244" t="s">
         <v>3</v>
@@ -4181,7 +4181,7 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B245" t="s">
         <v>3</v>
@@ -4189,7 +4189,7 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B246" t="s">
         <v>3</v>
@@ -4197,7 +4197,7 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B247" t="s">
         <v>3</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B248" t="s">
         <v>3</v>
@@ -4213,15 +4213,15 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B249" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B250" t="s">
         <v>3</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B251" t="s">
         <v>3</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B252" t="s">
         <v>3</v>
@@ -4245,15 +4245,15 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B253" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B254" t="s">
         <v>3</v>
@@ -4261,7 +4261,7 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B255" t="s">
         <v>3</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B256" t="s">
         <v>3</v>
@@ -4277,7 +4277,7 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B257" t="s">
         <v>3</v>
@@ -4285,7 +4285,7 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B258" t="s">
         <v>3</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B259" t="s">
         <v>3</v>
@@ -4301,7 +4301,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B260" t="s">
         <v>3</v>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B261" t="s">
         <v>3</v>
@@ -4317,7 +4317,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B262" t="s">
         <v>3</v>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B263" t="s">
         <v>3</v>
@@ -4333,7 +4333,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B264" t="s">
         <v>3</v>
@@ -4341,15 +4341,15 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B265" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B266" t="s">
         <v>3</v>
@@ -4357,15 +4357,15 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B267" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B268" t="s">
         <v>3</v>
@@ -4373,7 +4373,7 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B269" t="s">
         <v>3</v>
@@ -4381,7 +4381,7 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B270" t="s">
         <v>3</v>
@@ -4389,7 +4389,7 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B271" t="s">
         <v>3</v>
@@ -4397,7 +4397,7 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B272" t="s">
         <v>3</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B273" t="s">
         <v>3</v>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B274" t="s">
         <v>3</v>
@@ -4421,7 +4421,7 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B275" t="s">
         <v>3</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B276" t="s">
         <v>3</v>
@@ -4437,7 +4437,7 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B277" t="s">
         <v>3</v>
@@ -4445,7 +4445,7 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B278" t="s">
         <v>3</v>
@@ -4453,7 +4453,7 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B279" t="s">
         <v>3</v>
@@ -4461,15 +4461,15 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B280" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B281" t="s">
         <v>3</v>
@@ -4477,7 +4477,7 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B282" t="s">
         <v>3</v>
@@ -4485,7 +4485,7 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B283" t="s">
         <v>3</v>
@@ -4493,7 +4493,7 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B284" t="s">
         <v>3</v>
@@ -4501,31 +4501,31 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B285" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B286" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B287" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B288" t="s">
         <v>3</v>
@@ -4533,23 +4533,23 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B289" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B290" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B291" t="s">
         <v>3</v>
@@ -4557,7 +4557,7 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B292" t="s">
         <v>3</v>
@@ -4565,7 +4565,7 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B293" t="s">
         <v>3</v>
@@ -4573,15 +4573,15 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B294" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B295" t="s">
         <v>3</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B296" t="s">
         <v>3</v>
@@ -4597,7 +4597,7 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B297" t="s">
         <v>3</v>
@@ -4605,7 +4605,7 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B298" t="s">
         <v>3</v>
@@ -4613,7 +4613,7 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B299" t="s">
         <v>3</v>
@@ -4621,7 +4621,7 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B300" t="s">
         <v>3</v>
@@ -4629,23 +4629,23 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B301" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B302" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B303" t="s">
         <v>3</v>
@@ -4653,7 +4653,7 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B304" t="s">
         <v>3</v>
@@ -4661,7 +4661,7 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B305" t="s">
         <v>3</v>
@@ -4669,7 +4669,7 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B306" t="s">
         <v>3</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B307" t="s">
         <v>3</v>
@@ -4685,7 +4685,7 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B308" t="s">
         <v>3</v>
@@ -4693,15 +4693,15 @@
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B309" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B310" t="s">
         <v>3</v>
@@ -4709,7 +4709,7 @@
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B311" t="s">
         <v>3</v>
@@ -4717,7 +4717,7 @@
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B312" t="s">
         <v>3</v>
@@ -4725,7 +4725,7 @@
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B313" t="s">
         <v>3</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B314" t="s">
         <v>3</v>
@@ -4741,7 +4741,7 @@
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B315" t="s">
         <v>3</v>
@@ -4749,7 +4749,7 @@
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B316" t="s">
         <v>3</v>
@@ -4757,15 +4757,15 @@
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B317" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B318" t="s">
         <v>3</v>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B319" t="s">
         <v>3</v>
@@ -4781,7 +4781,7 @@
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B320" t="s">
         <v>3</v>
@@ -4789,15 +4789,15 @@
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B321" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B322" t="s">
         <v>3</v>
@@ -4805,7 +4805,7 @@
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B323" t="s">
         <v>3</v>
@@ -4813,15 +4813,15 @@
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B324" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B325" t="s">
         <v>3</v>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B326" t="s">
         <v>3</v>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B327" t="s">
         <v>3</v>
@@ -4845,10 +4845,10 @@
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B328" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -4856,7 +4856,7 @@
         <v>331</v>
       </c>
       <c r="B329" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -4864,7 +4864,7 @@
         <v>332</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="331">
@@ -4872,7 +4872,7 @@
         <v>333</v>
       </c>
       <c r="B331" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="332">
@@ -4880,7 +4880,7 @@
         <v>334</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="333">
@@ -4888,7 +4888,7 @@
         <v>335</v>
       </c>
       <c r="B333" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="334">
@@ -4896,7 +4896,7 @@
         <v>336</v>
       </c>
       <c r="B334" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="335">
@@ -4904,7 +4904,7 @@
         <v>337</v>
       </c>
       <c r="B335" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="336">
@@ -4912,7 +4912,7 @@
         <v>338</v>
       </c>
       <c r="B336" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="337">
@@ -4920,7 +4920,7 @@
         <v>339</v>
       </c>
       <c r="B337" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="338">
@@ -4928,7 +4928,7 @@
         <v>340</v>
       </c>
       <c r="B338" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="339">
@@ -4936,7 +4936,7 @@
         <v>341</v>
       </c>
       <c r="B339" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="340">
@@ -4944,7 +4944,7 @@
         <v>342</v>
       </c>
       <c r="B340" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="341">
@@ -4952,7 +4952,7 @@
         <v>343</v>
       </c>
       <c r="B341" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="342">
@@ -4960,7 +4960,7 @@
         <v>344</v>
       </c>
       <c r="B342" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="343">
@@ -4968,7 +4968,7 @@
         <v>345</v>
       </c>
       <c r="B343" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="344">
@@ -4976,7 +4976,7 @@
         <v>346</v>
       </c>
       <c r="B344" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="345">
@@ -4984,7 +4984,7 @@
         <v>347</v>
       </c>
       <c r="B345" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="346">
@@ -4992,7 +4992,7 @@
         <v>348</v>
       </c>
       <c r="B346" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="347">
@@ -5000,7 +5000,7 @@
         <v>349</v>
       </c>
       <c r="B347" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="348">
@@ -5008,7 +5008,7 @@
         <v>350</v>
       </c>
       <c r="B348" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="349">
@@ -5016,7 +5016,7 @@
         <v>351</v>
       </c>
       <c r="B349" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="350">
@@ -5024,7 +5024,7 @@
         <v>352</v>
       </c>
       <c r="B350" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="351">
@@ -5032,7 +5032,7 @@
         <v>353</v>
       </c>
       <c r="B351" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352">
@@ -5040,7 +5040,7 @@
         <v>354</v>
       </c>
       <c r="B352" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -5048,7 +5048,7 @@
         <v>355</v>
       </c>
       <c r="B353" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="354">
@@ -5056,7 +5056,7 @@
         <v>356</v>
       </c>
       <c r="B354" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="355">
@@ -5064,7 +5064,7 @@
         <v>357</v>
       </c>
       <c r="B355" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="356">
@@ -5072,7 +5072,7 @@
         <v>358</v>
       </c>
       <c r="B356" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="357">
@@ -5080,7 +5080,7 @@
         <v>359</v>
       </c>
       <c r="B357" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="358">
@@ -5088,7 +5088,7 @@
         <v>360</v>
       </c>
       <c r="B358" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="359">
@@ -5096,7 +5096,7 @@
         <v>361</v>
       </c>
       <c r="B359" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="360">
@@ -5104,7 +5104,7 @@
         <v>362</v>
       </c>
       <c r="B360" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="361">
@@ -5112,7 +5112,7 @@
         <v>363</v>
       </c>
       <c r="B361" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="362">
@@ -5120,7 +5120,7 @@
         <v>364</v>
       </c>
       <c r="B362" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="363">
@@ -5128,7 +5128,7 @@
         <v>365</v>
       </c>
       <c r="B363" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="364">
@@ -5136,7 +5136,7 @@
         <v>366</v>
       </c>
       <c r="B364" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="365">
@@ -5144,7 +5144,7 @@
         <v>367</v>
       </c>
       <c r="B365" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="366">
@@ -5152,7 +5152,7 @@
         <v>368</v>
       </c>
       <c r="B366" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="367">
@@ -5160,7 +5160,7 @@
         <v>369</v>
       </c>
       <c r="B367" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="368">
@@ -5168,7 +5168,7 @@
         <v>370</v>
       </c>
       <c r="B368" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -5176,7 +5176,7 @@
         <v>371</v>
       </c>
       <c r="B369" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="370">
@@ -5184,7 +5184,7 @@
         <v>372</v>
       </c>
       <c r="B370" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="371">
@@ -5192,7 +5192,7 @@
         <v>373</v>
       </c>
       <c r="B371" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="372">
@@ -5200,7 +5200,7 @@
         <v>374</v>
       </c>
       <c r="B372" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373">
@@ -5208,7 +5208,7 @@
         <v>375</v>
       </c>
       <c r="B373" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="374">
@@ -5216,7 +5216,7 @@
         <v>376</v>
       </c>
       <c r="B374" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="375">
@@ -5224,7 +5224,7 @@
         <v>377</v>
       </c>
       <c r="B375" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="376">
@@ -5232,7 +5232,7 @@
         <v>378</v>
       </c>
       <c r="B376" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="377">
@@ -5240,7 +5240,7 @@
         <v>379</v>
       </c>
       <c r="B377" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="378">
@@ -5248,7 +5248,7 @@
         <v>380</v>
       </c>
       <c r="B378" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="379">
@@ -5256,7 +5256,7 @@
         <v>381</v>
       </c>
       <c r="B379" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="380">
@@ -5264,7 +5264,7 @@
         <v>382</v>
       </c>
       <c r="B380" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="381">
@@ -5272,7 +5272,7 @@
         <v>383</v>
       </c>
       <c r="B381" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="382">
@@ -5280,7 +5280,7 @@
         <v>384</v>
       </c>
       <c r="B382" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="383">
@@ -5288,7 +5288,7 @@
         <v>385</v>
       </c>
       <c r="B383" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="384">
@@ -5296,7 +5296,7 @@
         <v>386</v>
       </c>
       <c r="B384" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
@@ -5304,7 +5304,7 @@
         <v>387</v>
       </c>
       <c r="B385" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="386">
@@ -5312,7 +5312,7 @@
         <v>388</v>
       </c>
       <c r="B386" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387">
@@ -5320,7 +5320,7 @@
         <v>389</v>
       </c>
       <c r="B387" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="388">
@@ -5328,7 +5328,7 @@
         <v>390</v>
       </c>
       <c r="B388" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="389">
@@ -5336,7 +5336,7 @@
         <v>391</v>
       </c>
       <c r="B389" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="390">
@@ -5344,7 +5344,7 @@
         <v>392</v>
       </c>
       <c r="B390" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391">
@@ -5352,7 +5352,7 @@
         <v>393</v>
       </c>
       <c r="B391" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="392">
@@ -5360,7 +5360,7 @@
         <v>394</v>
       </c>
       <c r="B392" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="393">
@@ -5368,7 +5368,7 @@
         <v>395</v>
       </c>
       <c r="B393" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="394">
@@ -5376,7 +5376,7 @@
         <v>396</v>
       </c>
       <c r="B394" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -5384,7 +5384,7 @@
         <v>397</v>
       </c>
       <c r="B395" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="396">
@@ -5392,7 +5392,7 @@
         <v>398</v>
       </c>
       <c r="B396" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="397">
@@ -5400,7 +5400,7 @@
         <v>399</v>
       </c>
       <c r="B397" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="398">
@@ -5408,7 +5408,7 @@
         <v>400</v>
       </c>
       <c r="B398" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="399">
@@ -5416,7 +5416,7 @@
         <v>401</v>
       </c>
       <c r="B399" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="400">
@@ -5424,7 +5424,7 @@
         <v>402</v>
       </c>
       <c r="B400" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="401">
@@ -5432,7 +5432,7 @@
         <v>403</v>
       </c>
       <c r="B401" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="402">
@@ -5440,7 +5440,7 @@
         <v>404</v>
       </c>
       <c r="B402" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="403">
@@ -5448,7 +5448,7 @@
         <v>405</v>
       </c>
       <c r="B403" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="404">
@@ -5456,7 +5456,7 @@
         <v>406</v>
       </c>
       <c r="B404" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405">
@@ -5464,7 +5464,7 @@
         <v>407</v>
       </c>
       <c r="B405" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="406">
@@ -5472,7 +5472,7 @@
         <v>408</v>
       </c>
       <c r="B406" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="407">
@@ -5480,7 +5480,7 @@
         <v>409</v>
       </c>
       <c r="B407" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -5488,7 +5488,7 @@
         <v>410</v>
       </c>
       <c r="B408" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -5496,7 +5496,7 @@
         <v>411</v>
       </c>
       <c r="B409" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -5504,7 +5504,7 @@
         <v>412</v>
       </c>
       <c r="B410" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="411">
@@ -5512,7 +5512,7 @@
         <v>413</v>
       </c>
       <c r="B411" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -5520,7 +5520,7 @@
         <v>414</v>
       </c>
       <c r="B412" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="413">
@@ -5528,7 +5528,7 @@
         <v>415</v>
       </c>
       <c r="B413" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="414">
@@ -5536,7 +5536,7 @@
         <v>416</v>
       </c>
       <c r="B414" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="415">
@@ -5544,7 +5544,7 @@
         <v>417</v>
       </c>
       <c r="B415" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="416">
@@ -5552,7 +5552,7 @@
         <v>418</v>
       </c>
       <c r="B416" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="417">
@@ -5560,7 +5560,7 @@
         <v>419</v>
       </c>
       <c r="B417" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418">
@@ -5568,7 +5568,7 @@
         <v>420</v>
       </c>
       <c r="B418" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419">
@@ -5576,7 +5576,7 @@
         <v>421</v>
       </c>
       <c r="B419" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="420">
@@ -5584,7 +5584,7 @@
         <v>422</v>
       </c>
       <c r="B420" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="421">
@@ -5592,7 +5592,7 @@
         <v>423</v>
       </c>
       <c r="B421" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="422">
@@ -5600,7 +5600,7 @@
         <v>424</v>
       </c>
       <c r="B422" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="423">
@@ -5608,7 +5608,7 @@
         <v>425</v>
       </c>
       <c r="B423" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="424">
@@ -5616,7 +5616,7 @@
         <v>426</v>
       </c>
       <c r="B424" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="425">
@@ -5624,7 +5624,7 @@
         <v>427</v>
       </c>
       <c r="B425" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426">
@@ -5632,7 +5632,7 @@
         <v>428</v>
       </c>
       <c r="B426" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="427">
@@ -5640,7 +5640,7 @@
         <v>429</v>
       </c>
       <c r="B427" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="428">
@@ -5648,7 +5648,7 @@
         <v>430</v>
       </c>
       <c r="B428" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="429">
@@ -5656,7 +5656,7 @@
         <v>431</v>
       </c>
       <c r="B429" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430">
@@ -5664,7 +5664,7 @@
         <v>432</v>
       </c>
       <c r="B430" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="431">
@@ -5672,7 +5672,7 @@
         <v>433</v>
       </c>
       <c r="B431" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="432">
@@ -5680,7 +5680,7 @@
         <v>434</v>
       </c>
       <c r="B432" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="433">
@@ -5688,7 +5688,7 @@
         <v>435</v>
       </c>
       <c r="B433" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
@@ -5696,7 +5696,7 @@
         <v>436</v>
       </c>
       <c r="B434" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="435">
@@ -5704,7 +5704,7 @@
         <v>437</v>
       </c>
       <c r="B435" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="436">
@@ -5712,7 +5712,7 @@
         <v>438</v>
       </c>
       <c r="B436" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="437">
@@ -5720,7 +5720,7 @@
         <v>439</v>
       </c>
       <c r="B437" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438">
@@ -5728,7 +5728,7 @@
         <v>440</v>
       </c>
       <c r="B438" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="439">
@@ -5736,7 +5736,7 @@
         <v>441</v>
       </c>
       <c r="B439" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="440">
@@ -5744,7 +5744,7 @@
         <v>442</v>
       </c>
       <c r="B440" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="441">
@@ -5752,7 +5752,7 @@
         <v>443</v>
       </c>
       <c r="B441" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="442">
@@ -5760,7 +5760,7 @@
         <v>444</v>
       </c>
       <c r="B442" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="443">
@@ -5768,7 +5768,7 @@
         <v>445</v>
       </c>
       <c r="B443" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="444">
@@ -5776,7 +5776,7 @@
         <v>446</v>
       </c>
       <c r="B444" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="445">
@@ -5784,7 +5784,7 @@
         <v>447</v>
       </c>
       <c r="B445" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="446">
@@ -5792,7 +5792,7 @@
         <v>448</v>
       </c>
       <c r="B446" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="447">
@@ -5800,7 +5800,7 @@
         <v>449</v>
       </c>
       <c r="B447" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448">
@@ -5808,7 +5808,7 @@
         <v>450</v>
       </c>
       <c r="B448" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="449">
@@ -5816,7 +5816,7 @@
         <v>451</v>
       </c>
       <c r="B449" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="450">
@@ -5824,7 +5824,7 @@
         <v>452</v>
       </c>
       <c r="B450" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="451">
@@ -5832,7 +5832,7 @@
         <v>453</v>
       </c>
       <c r="B451" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="452">
@@ -5840,7 +5840,7 @@
         <v>454</v>
       </c>
       <c r="B452" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="453">
@@ -5848,7 +5848,7 @@
         <v>455</v>
       </c>
       <c r="B453" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="454">
@@ -5856,7 +5856,7 @@
         <v>456</v>
       </c>
       <c r="B454" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="455">
@@ -5864,7 +5864,7 @@
         <v>457</v>
       </c>
       <c r="B455" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="456">
@@ -5872,7 +5872,7 @@
         <v>458</v>
       </c>
       <c r="B456" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="457">
@@ -5880,7 +5880,7 @@
         <v>459</v>
       </c>
       <c r="B457" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="458">
@@ -5888,7 +5888,7 @@
         <v>460</v>
       </c>
       <c r="B458" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459">
@@ -5896,7 +5896,7 @@
         <v>461</v>
       </c>
       <c r="B459" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="460">
@@ -5904,7 +5904,7 @@
         <v>462</v>
       </c>
       <c r="B460" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="461">
@@ -5912,7 +5912,7 @@
         <v>463</v>
       </c>
       <c r="B461" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="462">
@@ -5920,7 +5920,7 @@
         <v>464</v>
       </c>
       <c r="B462" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="463">
@@ -5928,7 +5928,7 @@
         <v>465</v>
       </c>
       <c r="B463" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="464">
@@ -5936,7 +5936,7 @@
         <v>466</v>
       </c>
       <c r="B464" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="465">
@@ -5944,7 +5944,7 @@
         <v>467</v>
       </c>
       <c r="B465" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="466">
@@ -5952,7 +5952,7 @@
         <v>468</v>
       </c>
       <c r="B466" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467">
@@ -5960,7 +5960,7 @@
         <v>469</v>
       </c>
       <c r="B467" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="468">
@@ -5968,7 +5968,7 @@
         <v>470</v>
       </c>
       <c r="B468" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="469">
@@ -5976,7 +5976,7 @@
         <v>471</v>
       </c>
       <c r="B469" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="470">
@@ -5984,7 +5984,7 @@
         <v>472</v>
       </c>
       <c r="B470" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="471">
@@ -5992,7 +5992,7 @@
         <v>473</v>
       </c>
       <c r="B471" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="472">
@@ -6000,7 +6000,7 @@
         <v>474</v>
       </c>
       <c r="B472" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="473">
@@ -6008,7 +6008,7 @@
         <v>475</v>
       </c>
       <c r="B473" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474">
@@ -6016,7 +6016,7 @@
         <v>476</v>
       </c>
       <c r="B474" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="475">
@@ -6024,7 +6024,7 @@
         <v>477</v>
       </c>
       <c r="B475" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="476">
@@ -6032,7 +6032,7 @@
         <v>478</v>
       </c>
       <c r="B476" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="477">
@@ -6040,7 +6040,7 @@
         <v>479</v>
       </c>
       <c r="B477" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="478">
@@ -6048,7 +6048,7 @@
         <v>480</v>
       </c>
       <c r="B478" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479">
@@ -6056,7 +6056,7 @@
         <v>481</v>
       </c>
       <c r="B479" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="480">
@@ -6064,7 +6064,7 @@
         <v>482</v>
       </c>
       <c r="B480" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="481">
@@ -6072,7 +6072,7 @@
         <v>483</v>
       </c>
       <c r="B481" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="482">
@@ -6080,7 +6080,7 @@
         <v>484</v>
       </c>
       <c r="B482" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="483">
@@ -6088,7 +6088,7 @@
         <v>485</v>
       </c>
       <c r="B483" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="484">
@@ -6096,7 +6096,7 @@
         <v>486</v>
       </c>
       <c r="B484" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="485">
@@ -6104,7 +6104,7 @@
         <v>487</v>
       </c>
       <c r="B485" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="486">
@@ -6112,7 +6112,7 @@
         <v>488</v>
       </c>
       <c r="B486" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="487">
@@ -6120,7 +6120,7 @@
         <v>489</v>
       </c>
       <c r="B487" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488">
@@ -6128,7 +6128,7 @@
         <v>490</v>
       </c>
       <c r="B488" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489">
@@ -6136,7 +6136,7 @@
         <v>491</v>
       </c>
       <c r="B489" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="490">
@@ -6144,7 +6144,7 @@
         <v>492</v>
       </c>
       <c r="B490" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="491">
@@ -6152,7 +6152,7 @@
         <v>493</v>
       </c>
       <c r="B491" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="492">
@@ -6160,7 +6160,7 @@
         <v>494</v>
       </c>
       <c r="B492" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="493">
@@ -6168,7 +6168,7 @@
         <v>495</v>
       </c>
       <c r="B493" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="494">
@@ -6176,7 +6176,7 @@
         <v>496</v>
       </c>
       <c r="B494" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="495">
@@ -6184,7 +6184,7 @@
         <v>497</v>
       </c>
       <c r="B495" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="496">
@@ -6192,7 +6192,7 @@
         <v>498</v>
       </c>
       <c r="B496" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497">
@@ -6200,7 +6200,7 @@
         <v>499</v>
       </c>
       <c r="B497" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="498">
@@ -6208,7 +6208,7 @@
         <v>500</v>
       </c>
       <c r="B498" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499">
@@ -6216,7 +6216,7 @@
         <v>501</v>
       </c>
       <c r="B499" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="500">
@@ -6224,7 +6224,7 @@
         <v>502</v>
       </c>
       <c r="B500" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="501">
@@ -6232,7 +6232,7 @@
         <v>503</v>
       </c>
       <c r="B501" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="502">
@@ -6240,7 +6240,7 @@
         <v>504</v>
       </c>
       <c r="B502" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="503">
@@ -6248,7 +6248,7 @@
         <v>505</v>
       </c>
       <c r="B503" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="504">
@@ -6256,7 +6256,7 @@
         <v>506</v>
       </c>
       <c r="B504" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505">
@@ -6264,7 +6264,7 @@
         <v>507</v>
       </c>
       <c r="B505" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506">
@@ -6272,7 +6272,7 @@
         <v>508</v>
       </c>
       <c r="B506" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="507">
@@ -6280,7 +6280,7 @@
         <v>509</v>
       </c>
       <c r="B507" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="508">
@@ -6288,7 +6288,7 @@
         <v>510</v>
       </c>
       <c r="B508" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="509">
@@ -6296,7 +6296,7 @@
         <v>511</v>
       </c>
       <c r="B509" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="510">
@@ -6304,7 +6304,7 @@
         <v>512</v>
       </c>
       <c r="B510" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="511">
@@ -6312,7 +6312,7 @@
         <v>513</v>
       </c>
       <c r="B511" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="512">
@@ -6320,7 +6320,7 @@
         <v>514</v>
       </c>
       <c r="B512" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="513">
@@ -6328,7 +6328,7 @@
         <v>515</v>
       </c>
       <c r="B513" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="514">
@@ -6336,7 +6336,7 @@
         <v>516</v>
       </c>
       <c r="B514" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515">
@@ -6344,7 +6344,7 @@
         <v>517</v>
       </c>
       <c r="B515" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="516">
@@ -6352,7 +6352,7 @@
         <v>518</v>
       </c>
       <c r="B516" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="517">
@@ -6360,7 +6360,7 @@
         <v>519</v>
       </c>
       <c r="B517" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="518">
@@ -6368,7 +6368,7 @@
         <v>520</v>
       </c>
       <c r="B518" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="519">
@@ -6376,7 +6376,7 @@
         <v>521</v>
       </c>
       <c r="B519" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="520">
@@ -6384,7 +6384,7 @@
         <v>522</v>
       </c>
       <c r="B520" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="521">
@@ -6392,7 +6392,7 @@
         <v>523</v>
       </c>
       <c r="B521" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="522">
@@ -6400,7 +6400,7 @@
         <v>524</v>
       </c>
       <c r="B522" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="523">
@@ -6408,7 +6408,7 @@
         <v>525</v>
       </c>
       <c r="B523" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
@@ -6416,7 +6416,7 @@
         <v>526</v>
       </c>
       <c r="B524" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="525">
@@ -6424,7 +6424,7 @@
         <v>527</v>
       </c>
       <c r="B525" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="526">
@@ -6432,7 +6432,7 @@
         <v>528</v>
       </c>
       <c r="B526" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="527">
@@ -6440,7 +6440,7 @@
         <v>529</v>
       </c>
       <c r="B527" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="528">
@@ -6448,7 +6448,7 @@
         <v>530</v>
       </c>
       <c r="B528" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="529">
@@ -6456,7 +6456,7 @@
         <v>531</v>
       </c>
       <c r="B529" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="530">
@@ -6464,7 +6464,7 @@
         <v>532</v>
       </c>
       <c r="B530" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="531">
@@ -6472,7 +6472,7 @@
         <v>533</v>
       </c>
       <c r="B531" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="532">
@@ -6480,7 +6480,7 @@
         <v>534</v>
       </c>
       <c r="B532" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
@@ -6488,7 +6488,7 @@
         <v>535</v>
       </c>
       <c r="B533" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="534">
@@ -6496,7 +6496,7 @@
         <v>536</v>
       </c>
       <c r="B534" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="535">
@@ -6504,7 +6504,7 @@
         <v>537</v>
       </c>
       <c r="B535" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="536">
@@ -6512,7 +6512,7 @@
         <v>538</v>
       </c>
       <c r="B536" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="537">
@@ -6520,7 +6520,7 @@
         <v>539</v>
       </c>
       <c r="B537" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538">
@@ -6528,7 +6528,7 @@
         <v>540</v>
       </c>
       <c r="B538" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="539">
@@ -6536,7 +6536,7 @@
         <v>541</v>
       </c>
       <c r="B539" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
@@ -6544,7 +6544,7 @@
         <v>542</v>
       </c>
       <c r="B540" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -6552,7 +6552,7 @@
         <v>543</v>
       </c>
       <c r="B541" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -6560,7 +6560,7 @@
         <v>544</v>
       </c>
       <c r="B542" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="543">
@@ -6568,7 +6568,7 @@
         <v>545</v>
       </c>
       <c r="B543" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="544">
@@ -6576,7 +6576,7 @@
         <v>546</v>
       </c>
       <c r="B544" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="545">
@@ -6584,7 +6584,7 @@
         <v>547</v>
       </c>
       <c r="B545" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="546">
@@ -6592,7 +6592,7 @@
         <v>548</v>
       </c>
       <c r="B546" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="547">
@@ -6600,7 +6600,7 @@
         <v>549</v>
       </c>
       <c r="B547" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="548">
@@ -6608,7 +6608,7 @@
         <v>550</v>
       </c>
       <c r="B548" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="549">
@@ -6616,7 +6616,7 @@
         <v>551</v>
       </c>
       <c r="B549" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550">
@@ -6624,7 +6624,7 @@
         <v>552</v>
       </c>
       <c r="B550" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="551">
@@ -6632,7 +6632,7 @@
         <v>553</v>
       </c>
       <c r="B551" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="552">
@@ -6640,7 +6640,7 @@
         <v>554</v>
       </c>
       <c r="B552" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="553">
@@ -6648,7 +6648,7 @@
         <v>555</v>
       </c>
       <c r="B553" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="554">
@@ -6656,7 +6656,7 @@
         <v>556</v>
       </c>
       <c r="B554" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="555">
@@ -6664,7 +6664,7 @@
         <v>557</v>
       </c>
       <c r="B555" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="556">
@@ -6672,7 +6672,7 @@
         <v>558</v>
       </c>
       <c r="B556" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557">
@@ -6680,7 +6680,7 @@
         <v>559</v>
       </c>
       <c r="B557" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -6688,7 +6688,7 @@
         <v>560</v>
       </c>
       <c r="B558" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
@@ -6696,7 +6696,7 @@
         <v>561</v>
       </c>
       <c r="B559" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
@@ -6704,7 +6704,7 @@
         <v>562</v>
       </c>
       <c r="B560" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -6712,7 +6712,7 @@
         <v>563</v>
       </c>
       <c r="B561" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="562">
@@ -6720,7 +6720,7 @@
         <v>564</v>
       </c>
       <c r="B562" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="563">
@@ -6728,7 +6728,7 @@
         <v>565</v>
       </c>
       <c r="B563" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="564">
@@ -6736,7 +6736,7 @@
         <v>566</v>
       </c>
       <c r="B564" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="565">
@@ -6744,7 +6744,7 @@
         <v>567</v>
       </c>
       <c r="B565" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="566">
@@ -6752,7 +6752,7 @@
         <v>568</v>
       </c>
       <c r="B566" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="567">
@@ -6760,7 +6760,7 @@
         <v>569</v>
       </c>
       <c r="B567" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="568">
@@ -6768,7 +6768,7 @@
         <v>570</v>
       </c>
       <c r="B568" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -6776,7 +6776,7 @@
         <v>571</v>
       </c>
       <c r="B569" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="570">
@@ -6784,7 +6784,7 @@
         <v>572</v>
       </c>
       <c r="B570" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="571">
@@ -6792,7 +6792,7 @@
         <v>573</v>
       </c>
       <c r="B571" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572">
@@ -6800,7 +6800,7 @@
         <v>574</v>
       </c>
       <c r="B572" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="573">
@@ -6808,7 +6808,7 @@
         <v>575</v>
       </c>
       <c r="B573" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="574">
@@ -6816,7 +6816,7 @@
         <v>576</v>
       </c>
       <c r="B574" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="575">
@@ -6824,7 +6824,7 @@
         <v>577</v>
       </c>
       <c r="B575" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="576">
@@ -6832,7 +6832,7 @@
         <v>578</v>
       </c>
       <c r="B576" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="577">
@@ -6840,7 +6840,7 @@
         <v>579</v>
       </c>
       <c r="B577" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="578">
@@ -6848,7 +6848,7 @@
         <v>580</v>
       </c>
       <c r="B578" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="579">
@@ -6856,7 +6856,7 @@
         <v>581</v>
       </c>
       <c r="B579" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="580">
@@ -6864,7 +6864,7 @@
         <v>582</v>
       </c>
       <c r="B580" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="581">
@@ -6872,7 +6872,7 @@
         <v>583</v>
       </c>
       <c r="B581" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="582">
@@ -6880,7 +6880,7 @@
         <v>584</v>
       </c>
       <c r="B582" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="583">
@@ -6888,7 +6888,7 @@
         <v>585</v>
       </c>
       <c r="B583" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="584">
@@ -6896,7 +6896,7 @@
         <v>586</v>
       </c>
       <c r="B584" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="585">
@@ -6904,7 +6904,7 @@
         <v>587</v>
       </c>
       <c r="B585" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="586">
@@ -6912,7 +6912,7 @@
         <v>588</v>
       </c>
       <c r="B586" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="587">
@@ -6920,7 +6920,7 @@
         <v>589</v>
       </c>
       <c r="B587" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="588">
@@ -6928,7 +6928,7 @@
         <v>590</v>
       </c>
       <c r="B588" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="589">
@@ -6936,7 +6936,7 @@
         <v>591</v>
       </c>
       <c r="B589" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="590">
@@ -6944,7 +6944,7 @@
         <v>592</v>
       </c>
       <c r="B590" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="591">
@@ -6952,7 +6952,7 @@
         <v>593</v>
       </c>
       <c r="B591" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="592">
@@ -6960,7 +6960,7 @@
         <v>594</v>
       </c>
       <c r="B592" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="593">
@@ -6968,7 +6968,7 @@
         <v>595</v>
       </c>
       <c r="B593" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="594">
@@ -6976,7 +6976,7 @@
         <v>596</v>
       </c>
       <c r="B594" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="595">
@@ -6984,7 +6984,7 @@
         <v>597</v>
       </c>
       <c r="B595" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="596">
@@ -6992,7 +6992,7 @@
         <v>598</v>
       </c>
       <c r="B596" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="597">
@@ -7000,7 +7000,7 @@
         <v>599</v>
       </c>
       <c r="B597" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="598">
@@ -7008,7 +7008,7 @@
         <v>600</v>
       </c>
       <c r="B598" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -7016,7 +7016,7 @@
         <v>601</v>
       </c>
       <c r="B599" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="600">
@@ -7024,7 +7024,7 @@
         <v>602</v>
       </c>
       <c r="B600" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="601">
@@ -7032,7 +7032,7 @@
         <v>603</v>
       </c>
       <c r="B601" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="602">
@@ -7040,7 +7040,7 @@
         <v>604</v>
       </c>
       <c r="B602" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="603">
@@ -7048,7 +7048,7 @@
         <v>605</v>
       </c>
       <c r="B603" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="604">
@@ -7056,7 +7056,7 @@
         <v>606</v>
       </c>
       <c r="B604" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="605">
@@ -7064,7 +7064,7 @@
         <v>607</v>
       </c>
       <c r="B605" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="606">
@@ -7072,7 +7072,7 @@
         <v>608</v>
       </c>
       <c r="B606" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="607">
@@ -7080,7 +7080,7 @@
         <v>609</v>
       </c>
       <c r="B607" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="608">
@@ -7088,7 +7088,7 @@
         <v>610</v>
       </c>
       <c r="B608" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="609">
@@ -7096,7 +7096,7 @@
         <v>611</v>
       </c>
       <c r="B609" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="610">
@@ -7104,7 +7104,7 @@
         <v>612</v>
       </c>
       <c r="B610" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="611">
@@ -7112,7 +7112,7 @@
         <v>613</v>
       </c>
       <c r="B611" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="612">
@@ -7120,7 +7120,7 @@
         <v>614</v>
       </c>
       <c r="B612" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="613">
@@ -7128,7 +7128,7 @@
         <v>615</v>
       </c>
       <c r="B613" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="614">
@@ -7136,7 +7136,7 @@
         <v>616</v>
       </c>
       <c r="B614" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="615">
@@ -7144,7 +7144,7 @@
         <v>617</v>
       </c>
       <c r="B615" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="616">
@@ -7152,7 +7152,7 @@
         <v>618</v>
       </c>
       <c r="B616" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="617">
@@ -7160,7 +7160,7 @@
         <v>619</v>
       </c>
       <c r="B617" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="618">
@@ -7168,7 +7168,7 @@
         <v>620</v>
       </c>
       <c r="B618" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="619">
@@ -7176,7 +7176,7 @@
         <v>621</v>
       </c>
       <c r="B619" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="620">
@@ -7184,7 +7184,7 @@
         <v>622</v>
       </c>
       <c r="B620" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="621">
@@ -7192,7 +7192,7 @@
         <v>623</v>
       </c>
       <c r="B621" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="622">
@@ -7200,7 +7200,7 @@
         <v>624</v>
       </c>
       <c r="B622" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
@@ -7208,7 +7208,7 @@
         <v>625</v>
       </c>
       <c r="B623" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="624">
@@ -7216,7 +7216,7 @@
         <v>626</v>
       </c>
       <c r="B624" t="s">
-        <v>330</v>
+        <v>6</v>
       </c>
     </row>
     <row r="625">
@@ -7224,7 +7224,7 @@
         <v>627</v>
       </c>
       <c r="B625" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
     <row r="626">
@@ -7232,7 +7232,7 @@
         <v>628</v>
       </c>
       <c r="B626" t="s">
-        <v>330</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Results/single_algorithm/CIMLR/CIMLR_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/single_algorithm/CIMLR/CIMLR_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">TCGA-AQ-A0Y5-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">CIMLRCIMLR1</t>
+    <t xml:space="preserve">CIMLR1</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA-EW-A2FW-01A</t>
@@ -32,7 +32,7 @@
     <t xml:space="preserve">TCGA-C8-A274-01A</t>
   </si>
   <si>
-    <t xml:space="preserve">CIMLRCIMLR2</t>
+    <t xml:space="preserve">CIMLR2</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA-B6-A0IK-01A</t>
